--- a/Files/Games-Players.xlsx
+++ b/Files/Games-Players.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\GitHub\UFMG\Disciplinas\DCC831-TECC_Teoria_dos_Jogos_em_Computacao-TP\Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0335E0C-F00E-4C35-BF5A-3A2961E55682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAA7610C-AD10-4301-8610-699495AE638A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8D6F93C0-AB8C-4D59-B58C-E3088606DB31}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{8D6F93C0-AB8C-4D59-B58C-E3088606DB31}"/>
   </bookViews>
   <sheets>
     <sheet name="Games" sheetId="1" r:id="rId1"/>
@@ -884,7 +884,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A27B51F5-1EC8-447E-A8B2-D9F89E9F4E15}">
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.109375" style="1" customWidth="1"/>
@@ -2268,17 +2268,55 @@
     <row r="101" spans="2:9" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="72">
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B98:B99"/>
+    <mergeCell ref="B85:D85"/>
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:D86"/>
+    <mergeCell ref="C87:D87"/>
+    <mergeCell ref="B88:B89"/>
+    <mergeCell ref="B90:B91"/>
+    <mergeCell ref="B93:D93"/>
+    <mergeCell ref="B94:B95"/>
+    <mergeCell ref="C94:D94"/>
+    <mergeCell ref="C95:D95"/>
+    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B79:B80"/>
+    <mergeCell ref="C77:E77"/>
+    <mergeCell ref="C78:E78"/>
+    <mergeCell ref="B81:B83"/>
+    <mergeCell ref="B76:E76"/>
+    <mergeCell ref="B71:B72"/>
+    <mergeCell ref="B73:B74"/>
+    <mergeCell ref="B77:B78"/>
+    <mergeCell ref="B63:B64"/>
+    <mergeCell ref="B65:B66"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="B69:B70"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="C70:D70"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B57:B58"/>
+    <mergeCell ref="B60:D60"/>
+    <mergeCell ref="B61:B62"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="B52:D52"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="C53:D53"/>
+    <mergeCell ref="C54:D54"/>
+    <mergeCell ref="B45:B46"/>
+    <mergeCell ref="C45:D45"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="B32:B33"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B40:B42"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="B44:D44"/>
     <mergeCell ref="B30:B31"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="B19:D19"/>
@@ -2291,55 +2329,17 @@
     <mergeCell ref="B28:B29"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="C29:D29"/>
-    <mergeCell ref="B45:B46"/>
-    <mergeCell ref="C45:D45"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B40:B42"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="B52:D52"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="C53:D53"/>
-    <mergeCell ref="C54:D54"/>
-    <mergeCell ref="B55:B56"/>
-    <mergeCell ref="B57:B58"/>
-    <mergeCell ref="B60:D60"/>
-    <mergeCell ref="B61:B62"/>
-    <mergeCell ref="C61:D61"/>
-    <mergeCell ref="C62:D62"/>
-    <mergeCell ref="B71:B72"/>
-    <mergeCell ref="B73:B74"/>
-    <mergeCell ref="B77:B78"/>
-    <mergeCell ref="B63:B64"/>
-    <mergeCell ref="B65:B66"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="B69:B70"/>
-    <mergeCell ref="C69:D69"/>
-    <mergeCell ref="C70:D70"/>
-    <mergeCell ref="B79:B80"/>
-    <mergeCell ref="C77:E77"/>
-    <mergeCell ref="C78:E78"/>
-    <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B76:E76"/>
-    <mergeCell ref="B98:B99"/>
-    <mergeCell ref="B85:D85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:D86"/>
-    <mergeCell ref="C87:D87"/>
-    <mergeCell ref="B88:B89"/>
-    <mergeCell ref="B90:B91"/>
-    <mergeCell ref="B93:D93"/>
-    <mergeCell ref="B94:B95"/>
-    <mergeCell ref="C94:D94"/>
-    <mergeCell ref="C95:D95"/>
-    <mergeCell ref="B96:B97"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="C4:D4"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2348,7 +2348,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AA3D14D3-44BC-4C71-9DAE-84F681775BBA}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" zeroHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
